--- a/data/trans_dic/P36$pan-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,98; 83,9</t>
+          <t>77,04; 83,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,13; 85,21</t>
+          <t>77,24; 84,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,0; 88,93</t>
+          <t>82,07; 89,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,02; 80,74</t>
+          <t>73,49; 80,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 81,98</t>
+          <t>74,05; 82,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,99; 86,97</t>
+          <t>79,86; 86,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,11; 81,44</t>
+          <t>76,18; 81,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,83; 82,21</t>
+          <t>76,81; 82,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,06; 86,97</t>
+          <t>82,21; 87,26</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,95; 80,12</t>
+          <t>74,25; 80,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,73; 79,57</t>
+          <t>72,93; 79,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,53; 86,82</t>
+          <t>80,75; 86,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,69; 79,73</t>
+          <t>73,22; 80,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,53; 83,15</t>
+          <t>76,39; 82,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,02; 88,18</t>
+          <t>82,22; 87,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,61; 79,4</t>
+          <t>74,56; 79,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,66; 80,41</t>
+          <t>75,46; 80,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,38; 86,62</t>
+          <t>82,21; 86,59</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,83; 76,32</t>
+          <t>68,88; 76,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,88; 82,3</t>
+          <t>75,89; 82,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,42; 83,56</t>
+          <t>77,28; 83,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,28; 79,73</t>
+          <t>73,45; 79,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,51; 86,43</t>
+          <t>80,27; 86,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,47; 89,53</t>
+          <t>84,33; 89,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,17; 77,14</t>
+          <t>72,15; 77,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>79,19; 83,52</t>
+          <t>78,98; 83,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,75; 85,74</t>
+          <t>81,91; 86,02</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,0; 78,4</t>
+          <t>69,95; 77,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,73; 83,49</t>
+          <t>76,45; 83,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,72; 85,12</t>
+          <t>79,26; 85,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,37; 81,47</t>
+          <t>74,24; 81,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,06; 86,39</t>
+          <t>79,72; 86,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,74</t>
+          <t>85,51; 90,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,21; 78,5</t>
+          <t>73,47; 78,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,03; 83,93</t>
+          <t>79,09; 83,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,21; 87,28</t>
+          <t>83,4; 87,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,68; 82,27</t>
+          <t>74,77; 82,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,33; 83,66</t>
+          <t>75,84; 83,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,4; 88,96</t>
+          <t>82,08; 88,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,01; 83,81</t>
+          <t>75,69; 83,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,24; 87,55</t>
+          <t>79,87; 87,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,88; 91,59</t>
+          <t>85,41; 91,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,72; 82,01</t>
+          <t>76,49; 82,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,29; 84,71</t>
+          <t>79,24; 84,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,9; 89,46</t>
+          <t>85,16; 89,8</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,09; 79,24</t>
+          <t>69,88; 79,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,81; 88,16</t>
+          <t>79,65; 88,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,26; 93,03</t>
+          <t>86,44; 92,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74,87; 83,14</t>
+          <t>74,63; 82,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79,61; 87,46</t>
+          <t>79,82; 87,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85,17; 91,49</t>
+          <t>84,97; 91,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,8; 80,38</t>
+          <t>73,63; 80,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,61; 86,45</t>
+          <t>80,67; 86,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86,82; 91,53</t>
+          <t>86,69; 91,43</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,27; 83,31</t>
+          <t>72,84; 83,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,05; 91,82</t>
+          <t>82,31; 91,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,06; 91,35</t>
+          <t>84,24; 91,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,32; 86,97</t>
+          <t>77,58; 86,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,21; 91,91</t>
+          <t>85,72; 92,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,09; 95,21</t>
+          <t>88,78; 95,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,49; 84,18</t>
+          <t>77,38; 84,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>85,48; 90,93</t>
+          <t>85,88; 91,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,98; 92,77</t>
+          <t>88,04; 92,7</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,98; 77,87</t>
+          <t>74,85; 77,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,62; 81,44</t>
+          <t>78,76; 81,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,13; 85,69</t>
+          <t>83,14; 85,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,77; 79,51</t>
+          <t>76,64; 79,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,58; 84,22</t>
+          <t>81,57; 84,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,45; 88,67</t>
+          <t>86,5; 88,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,3; 78,34</t>
+          <t>76,29; 78,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80,67; 82,55</t>
+          <t>80,52; 82,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>85,23; 86,92</t>
+          <t>85,21; 86,93</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>379636; 413759</t>
+          <t>379927; 413760</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>350295; 386987</t>
+          <t>350788; 383626</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343943; 373041</t>
+          <t>344256; 374313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>341366; 377434</t>
+          <t>343578; 378136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>315113; 351091</t>
+          <t>317115; 352569</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>315789; 343381</t>
+          <t>315303; 343022</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>731169; 782370</t>
+          <t>731853; 781400</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>677935; 725432</t>
+          <t>677759; 724837</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>668227; 708195</t>
+          <t>669414; 710519</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>543931; 589255</t>
+          <t>546094; 591291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>499014; 545958</t>
+          <t>500441; 545112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>475526; 512674</t>
+          <t>476832; 512997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>453139; 497054</t>
+          <t>456480; 499041</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>466159; 506463</t>
+          <t>465275; 505350</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>462207; 496933</t>
+          <t>463332; 495224</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1013880; 1079028</t>
+          <t>1013244; 1078808</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>979956; 1041443</t>
+          <t>977335; 1040851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>950704; 999635</t>
+          <t>948791; 999229</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>436897; 484473</t>
+          <t>437212; 482947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>515266; 558867</t>
+          <t>515298; 557523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>518044; 559100</t>
+          <t>517094; 560564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>505425; 549930</t>
+          <t>506642; 550525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>570765; 612683</t>
+          <t>569013; 610743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>558682; 592160</t>
+          <t>557750; 592238</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>955859; 1021768</t>
+          <t>955697; 1020487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1099142; 1159262</t>
+          <t>1096189; 1158571</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1087637; 1140803</t>
+          <t>1089806; 1144424</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>362061; 405479</t>
+          <t>361774; 403251</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>470779; 512283</t>
+          <t>469105; 510286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>506818; 548068</t>
+          <t>510327; 550705</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>382033; 418526</t>
+          <t>381345; 417930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>493311; 532351</t>
+          <t>491245; 531097</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>554751; 587942</t>
+          <t>554054; 587950</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>754697; 809308</t>
+          <t>757399; 811923</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>971841; 1032164</t>
+          <t>972655; 1030920</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1074931; 1127485</t>
+          <t>1077395; 1130871</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>288803; 318131</t>
+          <t>289140; 320587</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>323505; 359282</t>
+          <t>325680; 359287</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>393788; 425166</t>
+          <t>392264; 425261</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>307066; 338574</t>
+          <t>305764; 337678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>358502; 391137</t>
+          <t>356812; 389800</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>426694; 455064</t>
+          <t>424383; 456651</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>606608; 648416</t>
+          <t>604826; 649233</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>694725; 742264</t>
+          <t>694282; 744074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>827562; 872059</t>
+          <t>830136; 875311</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>202148; 231833</t>
+          <t>204467; 233392</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>244149; 273103</t>
+          <t>246750; 274075</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>288392; 311023</t>
+          <t>289008; 310030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>256741; 285113</t>
+          <t>255930; 284125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>281801; 309611</t>
+          <t>282575; 308413</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>321725; 345622</t>
+          <t>320994; 345495</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>468999; 510821</t>
+          <t>467907; 510851</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>535093; 573853</t>
+          <t>535475; 575540</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>618220; 651766</t>
+          <t>617303; 651072</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>153786; 174864</t>
+          <t>152884; 175649</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>204112; 228429</t>
+          <t>204761; 227851</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214529; 233147</t>
+          <t>214982; 233506</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>261528; 290406</t>
+          <t>259045; 289226</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>331461; 357505</t>
+          <t>333448; 358390</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>355461; 379845</t>
+          <t>354224; 379678</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>421363; 457778</t>
+          <t>420768; 457998</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>545135; 579882</t>
+          <t>547714; 580970</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>575583; 606865</t>
+          <t>575935; 606408</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2451660; 2546062</t>
+          <t>2447433; 2549606</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2689402; 2785872</t>
+          <t>2694410; 2788728</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2818298; 2905288</t>
+          <t>2818906; 2905461</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2591023; 2683720</t>
+          <t>2586715; 2685599</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2897809; 2991591</t>
+          <t>2897471; 2987930</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3061402; 3139965</t>
+          <t>3063207; 3145274</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5070013; 5205592</t>
+          <t>5069578; 5206523</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5625395; 5756348</t>
+          <t>5614404; 5748032</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5907625; 6024899</t>
+          <t>5906603; 6025465</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$pan-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,04; 83,9</t>
+          <t>76,74; 83,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,24; 84,47</t>
+          <t>76,92; 84,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,07; 89,24</t>
+          <t>81,94; 89,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,49; 80,89</t>
+          <t>73,31; 80,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,05; 82,33</t>
+          <t>74,25; 81,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,86; 86,88</t>
+          <t>79,61; 86,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,18; 81,34</t>
+          <t>76,11; 81,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,81; 82,15</t>
+          <t>76,88; 82,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,21; 87,26</t>
+          <t>82,15; 87,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,25; 80,39</t>
+          <t>74,11; 80,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,93; 79,45</t>
+          <t>72,75; 79,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,75; 86,88</t>
+          <t>80,25; 86,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,22; 80,05</t>
+          <t>73,34; 80,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,39; 82,97</t>
+          <t>76,01; 83,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,22; 87,88</t>
+          <t>82,15; 88,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,56; 79,39</t>
+          <t>74,82; 79,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,46; 80,36</t>
+          <t>75,32; 80,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,21; 86,59</t>
+          <t>82,23; 86,48</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,88; 76,08</t>
+          <t>68,99; 76,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,89; 82,11</t>
+          <t>75,61; 82,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,28; 83,78</t>
+          <t>77,64; 83,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,45; 79,82</t>
+          <t>73,01; 79,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,27; 86,15</t>
+          <t>80,45; 85,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,33; 89,54</t>
+          <t>84,79; 89,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,15; 77,05</t>
+          <t>72,03; 76,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,98; 83,47</t>
+          <t>79,14; 83,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,91; 86,02</t>
+          <t>81,97; 85,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,95; 77,97</t>
+          <t>70,32; 78,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,45; 83,17</t>
+          <t>76,68; 83,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,26; 85,53</t>
+          <t>79,11; 85,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,24; 81,36</t>
+          <t>73,82; 81,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,72; 86,19</t>
+          <t>79,83; 86,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,51; 90,74</t>
+          <t>85,39; 90,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,47; 78,76</t>
+          <t>73,53; 78,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,09; 83,83</t>
+          <t>79,33; 83,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,4; 87,54</t>
+          <t>83,26; 87,38</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,77; 82,9</t>
+          <t>74,55; 82,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,84; 83,67</t>
+          <t>75,85; 84,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,08; 88,98</t>
+          <t>82,32; 89,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75,69; 83,59</t>
+          <t>75,93; 83,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,87; 87,25</t>
+          <t>80,26; 87,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,41; 91,91</t>
+          <t>85,62; 91,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,49; 82,11</t>
+          <t>76,58; 82,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,24; 84,92</t>
+          <t>78,99; 84,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85,16; 89,8</t>
+          <t>85,17; 89,68</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,88; 79,77</t>
+          <t>69,65; 79,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,65; 88,47</t>
+          <t>79,4; 88,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,44; 92,73</t>
+          <t>86,4; 92,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74,63; 82,85</t>
+          <t>74,85; 82,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79,82; 87,12</t>
+          <t>79,55; 87,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,97; 91,46</t>
+          <t>84,86; 91,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,63; 80,38</t>
+          <t>73,86; 80,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,67; 86,71</t>
+          <t>80,76; 86,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,43</t>
+          <t>87,02; 91,36</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,84; 83,69</t>
+          <t>72,49; 83,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,31; 91,59</t>
+          <t>81,83; 91,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,24; 91,49</t>
+          <t>84,01; 91,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77,58; 86,62</t>
+          <t>77,72; 86,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,72; 92,14</t>
+          <t>85,4; 92,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,78; 95,16</t>
+          <t>89,03; 94,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,38; 84,22</t>
+          <t>77,26; 84,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>85,88; 91,1</t>
+          <t>85,33; 90,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88,04; 92,7</t>
+          <t>87,91; 92,77</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,85; 77,97</t>
+          <t>74,97; 77,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,76; 81,52</t>
+          <t>78,81; 81,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,14; 85,7</t>
+          <t>83,23; 85,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,64; 79,57</t>
+          <t>76,73; 79,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,57; 84,12</t>
+          <t>81,59; 84,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,5; 88,82</t>
+          <t>86,42; 88,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,29; 78,35</t>
+          <t>76,21; 78,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80,52; 82,43</t>
+          <t>80,55; 82,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>85,21; 86,93</t>
+          <t>85,25; 86,85</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>379927; 413760</t>
+          <t>378449; 412627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>350788; 383626</t>
+          <t>349321; 383549</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>344256; 374313</t>
+          <t>343717; 374012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>343578; 378136</t>
+          <t>342719; 377313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>317115; 352569</t>
+          <t>317980; 350787</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>315303; 343022</t>
+          <t>314326; 342319</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>731853; 781400</t>
+          <t>731146; 781897</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>677759; 724837</t>
+          <t>678374; 724386</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>669414; 710519</t>
+          <t>668935; 710773</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>546094; 591291</t>
+          <t>545040; 589979</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>500441; 545112</t>
+          <t>499151; 544720</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476832; 512997</t>
+          <t>473861; 511964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>456480; 499041</t>
+          <t>457226; 499440</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>465275; 505350</t>
+          <t>462946; 505783</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>463332; 495224</t>
+          <t>462926; 495903</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1013244; 1078808</t>
+          <t>1016776; 1077128</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>977335; 1040851</t>
+          <t>975517; 1041291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>948791; 999229</t>
+          <t>948991; 998000</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>437212; 482947</t>
+          <t>437924; 483288</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>515298; 557523</t>
+          <t>513427; 557214</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>517094; 560564</t>
+          <t>519490; 559762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>506642; 550525</t>
+          <t>503606; 548621</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>569013; 610743</t>
+          <t>570318; 609490</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>557750; 592238</t>
+          <t>560788; 594894</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>955697; 1020487</t>
+          <t>954055; 1017378</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1096189; 1158571</t>
+          <t>1098470; 1157680</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1089806; 1144424</t>
+          <t>1090531; 1141662</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>361774; 403251</t>
+          <t>363710; 404313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>469105; 510286</t>
+          <t>470508; 510778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>510327; 550705</t>
+          <t>509336; 548664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>381345; 417930</t>
+          <t>379205; 417475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>491245; 531097</t>
+          <t>491903; 532283</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>554054; 587950</t>
+          <t>553274; 586696</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>757399; 811923</t>
+          <t>758022; 814231</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>972655; 1030920</t>
+          <t>975636; 1032760</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1077395; 1130871</t>
+          <t>1075580; 1128844</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>289140; 320587</t>
+          <t>288291; 320289</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>325680; 359287</t>
+          <t>325715; 361387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>392264; 425261</t>
+          <t>393424; 426407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>305764; 337678</t>
+          <t>306754; 337588</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>356812; 389800</t>
+          <t>358567; 390731</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>424383; 456651</t>
+          <t>425412; 455471</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>604826; 649233</t>
+          <t>605519; 648896</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>694282; 744074</t>
+          <t>692076; 740773</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>830136; 875311</t>
+          <t>830230; 874153</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>204467; 233392</t>
+          <t>203774; 233373</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>246750; 274075</t>
+          <t>245986; 273995</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>289008; 310030</t>
+          <t>288847; 310715</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255930; 284125</t>
+          <t>256701; 283621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>282575; 308413</t>
+          <t>281615; 310387</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>320994; 345495</t>
+          <t>320583; 345864</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>467907; 510851</t>
+          <t>469369; 510562</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>535475; 575540</t>
+          <t>536083; 576313</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>617303; 651072</t>
+          <t>619680; 650550</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>152884; 175649</t>
+          <t>152154; 175318</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>204761; 227851</t>
+          <t>203569; 226869</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214982; 233506</t>
+          <t>214407; 232399</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>259045; 289226</t>
+          <t>259528; 289326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>333448; 358390</t>
+          <t>332207; 357853</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>354224; 379678</t>
+          <t>355208; 378985</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>420768; 457998</t>
+          <t>420125; 456889</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>547714; 580970</t>
+          <t>544220; 580080</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>575935; 606408</t>
+          <t>575119; 606867</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2447433; 2549606</t>
+          <t>2451542; 2544753</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2694410; 2788728</t>
+          <t>2695955; 2793756</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2818906; 2905461</t>
+          <t>2821863; 2902886</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2586715; 2685599</t>
+          <t>2589879; 2683530</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2897471; 2987930</t>
+          <t>2898251; 2988337</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3063207; 3145274</t>
+          <t>3060392; 3139268</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5069578; 5206523</t>
+          <t>5064353; 5203467</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5614404; 5748032</t>
+          <t>5616549; 5749723</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5906603; 6025465</t>
+          <t>5909064; 6020041</t>
         </is>
       </c>
     </row>
